--- a/CSCI_2020_TRANSCRIPT.xlsx
+++ b/CSCI_2020_TRANSCRIPT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VSU Computer Science\Documents\autoadvisor-main v2\autoadvisor-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\terre\AppData\Local\Temp\MicrosoftEdgeDownloads\4ce7b78c-5fb2-411b-a6f7-15bc1aabaa64\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68CBCCD5-716A-4D21-8D9D-58C7ADE930D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140D9EFB-42DF-4234-A948-ECB1E5BA42CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14895" yWindow="2175" windowWidth="16410" windowHeight="15345" xr2:uid="{512055B1-4831-4ADE-89A2-67DFDBC3B196}"/>
+    <workbookView xWindow="2580" yWindow="2580" windowWidth="19200" windowHeight="11170" xr2:uid="{512055B1-4831-4ADE-89A2-67DFDBC3B196}"/>
   </bookViews>
   <sheets>
     <sheet name="planning_sheet" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="132">
   <si>
     <t>Course</t>
   </si>
@@ -416,12 +416,6 @@
     <t>SPAN, FREN, GERM, ARTS 199, PHIL 314, GEOG 210, MUSI 199, DRAM 199, AGRI 295, ENGL 214, HIST 114, HIST 115</t>
   </si>
   <si>
-    <t>&lt;BIOL 121: BIOL120&gt;, &lt;CHEM 152: CHEM 151&gt;, &lt;PHYS 106: PHYS 105&gt;, &lt;PHYS 113: PHYS 112&gt;</t>
-  </si>
-  <si>
-    <t>&lt;BIOL 121: BIOL120&gt;, &lt;CHEM 154: CHEM 153&gt;, &lt;PHYS 106: PHYS 105&gt;, &lt;PHYS 113: PHYS 112&gt;</t>
-  </si>
-  <si>
     <t>BIOL 120, BIOL 121, BIOL 319, CHEM 151, CHEM 152, PHYS 105, PHYS 106, PHYS 112, PHYS 113</t>
   </si>
   <si>
@@ -435,6 +429,9 @@
   </si>
   <si>
     <t>CSCI 312, CSCI 361, CSCI 389, CSCI 396, CSCI 402, CSCI 450, CSCI 451, CSCI 453, CSCI 457, CSCI 460, CSCI 495, CSCI 496</t>
+  </si>
+  <si>
+    <t>&lt;BIOL 121: BIOL120&gt;, &lt;CHEM 152: CHEM 151&gt;, &lt;PHYS 106: PHYS 105&gt;, &lt;PHYS112: MATH 260&gt;, &lt;PHYS 113: PHYS 112&gt;</t>
   </si>
 </sst>
 </file>
@@ -787,22 +784,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8CACD1-7A2B-42FB-A662-1A1D7F764097}">
   <dimension ref="A1:L44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7265625" customWidth="1"/>
+    <col min="12" max="12" width="19.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>8</v>
       </c>
@@ -837,7 +834,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -857,7 +854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -877,7 +874,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>9</v>
       </c>
@@ -897,7 +894,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -917,7 +914,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -937,7 +934,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>9</v>
       </c>
@@ -954,7 +951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -977,7 +974,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>9</v>
       </c>
@@ -1000,7 +997,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>9</v>
       </c>
@@ -1023,7 +1020,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>9</v>
       </c>
@@ -1046,7 +1043,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>10</v>
       </c>
@@ -1066,7 +1063,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1086,7 +1083,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1109,7 +1106,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>9</v>
       </c>
@@ -1129,7 +1126,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>9</v>
       </c>
@@ -1149,7 +1146,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>9</v>
       </c>
@@ -1169,7 +1166,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>9</v>
       </c>
@@ -1192,7 +1189,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -1218,7 +1215,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>9</v>
       </c>
@@ -1238,7 +1235,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>9</v>
       </c>
@@ -1258,7 +1255,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>9</v>
       </c>
@@ -1278,7 +1275,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>9</v>
       </c>
@@ -1298,7 +1295,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -1324,7 +1321,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>9</v>
       </c>
@@ -1344,7 +1341,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>9</v>
       </c>
@@ -1364,7 +1361,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>9</v>
       </c>
@@ -1384,7 +1381,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>10</v>
       </c>
@@ -1404,13 +1401,13 @@
         <v>69</v>
       </c>
       <c r="K28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>10</v>
       </c>
@@ -1430,13 +1427,13 @@
         <v>68</v>
       </c>
       <c r="K29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L29" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>84</v>
       </c>
@@ -1459,13 +1456,13 @@
         <v>48</v>
       </c>
       <c r="K30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>9</v>
       </c>
@@ -1485,7 +1482,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>9</v>
       </c>
@@ -1502,10 +1499,10 @@
         <v>3</v>
       </c>
       <c r="H32" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>9</v>
       </c>
@@ -1528,7 +1525,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>11</v>
       </c>
@@ -1545,7 +1542,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>93</v>
       </c>
@@ -1568,7 +1565,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>10</v>
       </c>
@@ -1588,10 +1585,10 @@
         <v>48</v>
       </c>
       <c r="K36" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>11</v>
       </c>
@@ -1608,7 +1605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>9</v>
       </c>
@@ -1631,7 +1628,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>10</v>
       </c>
@@ -1651,13 +1648,13 @@
         <v>104</v>
       </c>
       <c r="K39" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L39" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>10</v>
       </c>
@@ -1677,13 +1674,13 @@
         <v>103</v>
       </c>
       <c r="K40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L40" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>105</v>
       </c>
@@ -1709,7 +1706,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>10</v>
       </c>
@@ -1729,10 +1726,10 @@
         <v>48</v>
       </c>
       <c r="K42" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>9</v>
       </c>
@@ -1752,7 +1749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>9</v>
       </c>
